--- a/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34558180-4906-4030-B701-505E0627FF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D504ECD4-EAED-4174-9D40-10EFD55AB612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7010" yWindow="1890" windowWidth="14560" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29430" yWindow="6480" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="珊瑚礁海域" sheetId="1" r:id="rId1"/>
+    <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>硬质纤维</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,6 +105,9 @@
   </si>
   <si>
     <t>Progress</t>
+  </si>
+  <si>
+    <t>韧性胶管</t>
   </si>
 </sst>
 </file>
@@ -468,33 +467,33 @@
         <v>0</v>
       </c>
       <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>21</v>
-      </c>
-      <c r="O1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -715,7 +714,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>2</v>

--- a/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D504ECD4-EAED-4174-9D40-10EFD55AB612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE59C78-11DF-4247-A982-780F1CC04769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29430" yWindow="6480" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
+    <sheet name="PhosphorTomb" sheetId="2" r:id="rId2"/>
+    <sheet name="SpaceshipOuterHull" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
   <si>
     <t>SizeChangeOnNotCaught</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,18 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>水瓶鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱情贝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虹吸海葵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DropNum</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,6 +98,46 @@
   </si>
   <si>
     <t>韧性胶管</t>
+  </si>
+  <si>
+    <t>海麻线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海麻线丛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有产物的虹吸海葵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻璃沙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白爆矿堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有产物的水瓶鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>废料堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性胶管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碳素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有产物的爱情贝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -433,23 +463,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.4140625" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -467,33 +497,33 @@
         <v>0</v>
       </c>
       <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -520,9 +550,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -552,9 +582,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -584,9 +614,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -616,9 +646,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -648,9 +678,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -662,7 +692,7 @@
         <v>15000</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>-1000</v>
@@ -680,9 +710,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -712,9 +742,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -741,6 +771,616 @@
         <v>0</v>
       </c>
       <c r="N9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC5C559A-969E-4738-9F1B-CA6C3A13C8F6}">
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>10000</v>
+      </c>
+      <c r="E2">
+        <v>-6</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3000</v>
+      </c>
+      <c r="D3">
+        <v>5000</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>-1000</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>5000</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>-1000</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2000</v>
+      </c>
+      <c r="D5">
+        <v>4000</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>-1000</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>4000</v>
+      </c>
+      <c r="D6">
+        <v>15000</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>-1000</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>6000</v>
+      </c>
+      <c r="D7">
+        <v>15000</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>-1000</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
+      </c>
+      <c r="D8">
+        <v>5000</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>-1000</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>4000</v>
+      </c>
+      <c r="D9">
+        <v>15000</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>-1000</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019EE8E2-3B63-47F7-870D-89106ADC9B94}">
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>10000</v>
+      </c>
+      <c r="E2">
+        <v>-6</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2000</v>
+      </c>
+      <c r="D3">
+        <v>4000</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>-1000</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2000</v>
+      </c>
+      <c r="D4">
+        <v>5000</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>-1000</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>6000</v>
+      </c>
+      <c r="D5">
+        <v>15000</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>-1000</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>6000</v>
+      </c>
+      <c r="D6">
+        <v>15000</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>-1000</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>3000</v>
+      </c>
+      <c r="D7">
+        <v>15000</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>-1000</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>4000</v>
+      </c>
+      <c r="D8">
+        <v>10000</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>-1000</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE59C78-11DF-4247-A982-780F1CC04769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3282AE-F53D-403B-833A-F5F6B7FA42EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,11 +132,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>碳素</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>有产物的爱情贝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃素</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -584,7 +584,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>1</v>

--- a/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
@@ -1,174 +1,491 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3282AE-F53D-403B-833A-F5F6B7FA42EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
     <sheet name="PhosphorTomb" sheetId="2" r:id="rId2"/>
     <sheet name="SpaceshipOuterHull" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
+  <si>
+    <t>CardId</t>
+  </si>
+  <si>
+    <t>DropNum</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>MaxSize</t>
+  </si>
+  <si>
+    <t>SizeChangePerRound</t>
+  </si>
+  <si>
+    <t>SizeChangeOnCaught</t>
+  </si>
   <si>
     <t>SizeChangeOnNotCaught</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxSize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SizeChangePerRound</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SizeChangeOnCaught</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DropNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OverwriteFreshness</t>
+  </si>
+  <si>
+    <t>Freshness</t>
+  </si>
+  <si>
+    <t>OverwriteDurability</t>
+  </si>
+  <si>
+    <t>Durability</t>
+  </si>
+  <si>
+    <t>OverwriteGrowth</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>OverwriteProgress</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Trappable</t>
+  </si>
+  <si>
+    <t>空</t>
+  </si>
+  <si>
+    <t>有产物的水瓶鱼</t>
+  </si>
+  <si>
+    <t>有产物的爱情贝</t>
+  </si>
+  <si>
+    <t>有产物的虹吸海葵</t>
   </si>
   <si>
     <t>珊瑚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>白爆矿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>废金属</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OverwriteFreshness</t>
-  </si>
-  <si>
-    <t>Freshness</t>
-  </si>
-  <si>
-    <t>OverwriteDurability</t>
-  </si>
-  <si>
-    <t>Durability</t>
-  </si>
-  <si>
-    <t>OverwriteGrowth</t>
-  </si>
-  <si>
-    <t>Growth</t>
-  </si>
-  <si>
-    <t>OverwriteProgress</t>
-  </si>
-  <si>
-    <t>Progress</t>
   </si>
   <si>
     <t>韧性胶管</t>
   </si>
   <si>
     <t>海麻线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>海麻线丛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有产物的虹吸海葵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>玻璃沙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>白爆矿堆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有产物的水瓶鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>废料堆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>韧性胶管</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有产物的爱情贝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>燃素</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -176,24 +493,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -242,7 +845,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -277,7 +880,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -451,79 +1054,77 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="11.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="5.11111111111111" customWidth="1"/>
+    <col min="4" max="4" width="7.55555555555556" customWidth="1"/>
+    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="19.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
-      </c>
-      <c r="N1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -549,10 +1150,13 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -581,10 +1185,13 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -613,10 +1220,13 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -645,10 +1255,13 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -677,10 +1290,13 @@
       <c r="N6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -709,10 +1325,13 @@
       <c r="N7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -741,10 +1360,13 @@
       <c r="N8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -773,78 +1395,86 @@
       <c r="N9" t="b">
         <v>0</v>
       </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC5C559A-969E-4738-9F1B-CA6C3A13C8F6}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="11.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="5.11111111111111" customWidth="1"/>
+    <col min="4" max="4" width="7.55555555555556" customWidth="1"/>
+    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="19.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
+    <col min="14" max="14" width="13.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
-      </c>
-      <c r="N1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -870,10 +1500,13 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -902,10 +1535,13 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -934,10 +1570,13 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -966,10 +1605,13 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -998,10 +1640,13 @@
       <c r="N6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1030,10 +1675,13 @@
       <c r="N7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1062,10 +1710,13 @@
       <c r="N8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1094,78 +1745,85 @@
       <c r="N9" t="b">
         <v>0</v>
       </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019EE8E2-3B63-47F7-870D-89106ADC9B94}">
-  <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="11.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="5.55555555555556" customWidth="1"/>
+    <col min="4" max="4" width="7.55555555555556" customWidth="1"/>
+    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="19.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
-      </c>
-      <c r="N1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -1191,10 +1849,13 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1223,10 +1884,13 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1255,10 +1919,13 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -1287,10 +1954,13 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1319,10 +1989,13 @@
       <c r="N6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1351,8 +2024,11 @@
       <c r="N7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1383,10 +2059,13 @@
       <c r="N8" t="b">
         <v>0</v>
       </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B520CB7-15E8-4E8D-AF02-88BD8703257F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
@@ -12,19 +18,6 @@
     <sheet name="SpaceshipOuterHull" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -124,14 +117,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,352 +127,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -493,310 +150,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1054,25 +425,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="5.11111111111111" customWidth="1"/>
-    <col min="4" max="4" width="7.55555555555556" customWidth="1"/>
-    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="19.1111111111111" customWidth="1"/>
-    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1154,7 +525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1186,10 +557,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1221,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1256,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1294,7 +665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1329,7 +700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1364,7 +735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1400,29 +771,28 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="5.11111111111111" customWidth="1"/>
-    <col min="4" max="4" width="7.55555555555556" customWidth="1"/>
-    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="19.1111111111111" customWidth="1"/>
-    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
-    <col min="14" max="14" width="13.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1472,7 +842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1504,7 +874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1539,7 +909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1609,7 +979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1644,7 +1014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1679,7 +1049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1714,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1750,28 +1120,27 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="5.55555555555556" customWidth="1"/>
-    <col min="4" max="4" width="7.55555555555556" customWidth="1"/>
-    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="19.1111111111111" customWidth="1"/>
-    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1821,7 +1190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1853,7 +1222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1885,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1923,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1958,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1993,7 +1362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2028,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -2064,8 +1433,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B520CB7-15E8-4E8D-AF02-88BD8703257F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5D61B0-BF67-4A2E-920D-A1E29C29DC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,11 @@
     <sheet name="SpaceshipOuterHull" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -432,18 +437,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="5.125" customWidth="1"/>
+    <col min="4" max="4" width="7.5" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +498,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -525,7 +530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -560,7 +565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -595,7 +600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -630,7 +635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -665,7 +670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -700,7 +705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -735,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -780,19 +785,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="5.125" customWidth="1"/>
+    <col min="4" max="4" width="7.5" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -842,7 +847,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -874,7 +879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -909,7 +914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -944,7 +949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -976,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1014,7 +1019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1049,7 +1054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1084,7 +1089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1129,18 +1134,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="5.5" customWidth="1"/>
+    <col min="4" max="4" width="7.5" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1190,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1222,7 +1227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1257,7 +1262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1292,7 +1297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1327,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1362,7 +1367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1397,7 +1402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>29</v>
       </c>

--- a/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/RepeatableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5D61B0-BF67-4A2E-920D-A1E29C29DC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C69B06A-BE40-4C2B-9852-248EF0364EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="31">
   <si>
     <t>CardId</t>
   </si>
@@ -117,13 +117,17 @@
   </si>
   <si>
     <t>燃素</t>
+  </si>
+  <si>
+    <t>水壶兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +137,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -159,8 +171,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -437,18 +450,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="5.125" customWidth="1"/>
-    <col min="4" max="4" width="7.5" customWidth="1"/>
-    <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="19.125" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -530,7 +543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -565,7 +578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -600,7 +613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -635,7 +648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -670,7 +683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -705,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -740,7 +753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -784,20 +797,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="5.125" customWidth="1"/>
-    <col min="4" max="4" width="7.5" customWidth="1"/>
-    <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="19.125" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
-    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -847,7 +860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -879,7 +892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -914,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -949,7 +962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -984,7 +997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -998,7 +1011,7 @@
         <v>15000</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>-1000</v>
@@ -1019,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1030,7 +1043,7 @@
         <v>6000</v>
       </c>
       <c r="D7">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="E7">
         <v>13</v>
@@ -1054,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1089,7 +1102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1121,6 +1134,41 @@
         <v>0</v>
       </c>
       <c r="P9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1000</v>
+      </c>
+      <c r="D10">
+        <v>5000</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>-1000</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1133,19 +1181,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="5.5" customWidth="1"/>
-    <col min="4" max="4" width="7.5" customWidth="1"/>
-    <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="19.125" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="5.44140625" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1227,7 +1275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1262,7 +1310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1297,7 +1345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1332,7 +1380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1367,7 +1415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1402,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1416,7 +1464,7 @@
         <v>10000</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>-1000</v>
@@ -1435,6 +1483,41 @@
       </c>
       <c r="P8" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>3000</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>-1000</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
